--- a/data.xlsx
+++ b/data.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¨ظ† طµط§ظ„ط­ ط§ظ„طµظ†ط§طھ</t>
+          <t>فارس عبدالعزيز بن صالح الصنات</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¨ظ† طµط§ظ„ط­ ط§ظ„طµظ†ط§طھ</t>
+          <t>فارس عبدالعزيز بن صالح الصنات</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¨ظ† طµط§ظ„ط­ ط§ظ„طµظ†ط§طھ</t>
+          <t>فارس عبدالعزيز بن صالح الصنات</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¨ظ† طµط§ظ„ط­ ط§ظ„طµظ†ط§طھ</t>
+          <t>فارس عبدالعزيز بن صالح الصنات</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ط¹ظ„ظٹ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>علي مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1011,7 +1011,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ط³ط¹ظˆط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>يوسف سعود بن صالح الحربي</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1122,7 +1122,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>عزام خالد بن علي الدخيل</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ط£ظ…ط¬ط¯ ظ…ط­ظ…ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط´ط±ط§ط­ظٹظ„ظٹ</t>
+          <t>أمجد محمد بن عبدالله شراحيلي</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1862,7 +1862,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ظ…ط§ط¬ط¯ طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>اياد ماجد صالح المحيسن</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2084,7 +2084,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>باسم عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2158,7 +2158,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ثامر محمد عبدالله الحربي</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-1</t>
+          <t>ثقافة إسلامية-1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2602,7 +2602,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط¹ط¨ط¯ ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط§ظ„ط¬ط¯ط¹ط§ظ†</t>
+          <t>ريان عبد الله صالح الجدعان</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2676,7 +2676,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2713,7 +2713,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2750,7 +2750,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2787,7 +2787,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2824,7 +2824,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ط¹ط´ظˆط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط´ظˆط§ظ† ط§ظ„ط¹ط´ظˆط§ظ†</t>
+          <t>عشوان عبدالله بن عشوان العشوان</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2972,7 +2972,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3120,7 +3120,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط³ظ„ظ…ط§ظ† ط¸ط§ظپط± ط§ظ„ظ‚ط­ط·ط§ظ†ظٹ</t>
+          <t>مازن سلمان ظافر القحطاني</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3194,7 +3194,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3231,7 +3231,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط³ط¹ظˆط¯ ط§ظ„ط¹ط´ط±ظ‡</t>
+          <t>فارس عبدالرحمن بن سعود العشره</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3416,7 +3416,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3564,7 +3564,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ظ…ط´ط§ط±ظٹط¹ ط¥ظ†طھط§ط¬ظٹط©</t>
+          <t>مشاريع إنتاجية</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ط¹ظٹط¯ ط´ط¬ط§ط¹ ط¨ظ† ط¹ظٹط¯ ط§ظ„ط¹ط±ظ…ط§ظ†ظٹ</t>
+          <t>عيد شجاع بن عيد العرماني</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3675,7 +3675,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3749,7 +3749,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3786,7 +3786,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ظ…ط´ط§ط±ظٹط¹ ط¥ظ†طھط§ط¬ظٹط©</t>
+          <t>مشاريع إنتاجية</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظˆظ‡ط§ط¨ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط­ظ…ط¯ ط§ظ„ط°ظٹط§ط¨</t>
+          <t>عبدالوهاب عبدالعزيز حمد الذياب</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4008,7 +4008,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4156,7 +4156,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4193,7 +4193,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط¬ط±ط¨ظˆط¹</t>
+          <t>محمد عبدالله بن محمد الجربوع</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4230,7 +4230,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4304,7 +4304,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4341,7 +4341,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4452,7 +4452,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ظ…ط´ط§ط±ظٹط¹ ط¥ظ†طھط§ط¬ظٹط©</t>
+          <t>مشاريع إنتاجية</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ظ…ظٹط³ ظ†ظ‚ط§ط، ط§ظ„ط³ط¹ط¯ظٹ</t>
+          <t>تركي خميس نقاء السعدي</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4563,7 +4563,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4600,7 +4600,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4674,7 +4674,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ظ…ط´ط§ط±ظٹط¹ ط¥ظ†طھط§ط¬ظٹط©</t>
+          <t>مشاريع إنتاجية</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ظ…ط§ط¬ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط«ظ†ظٹط§ظ†</t>
+          <t>صالح ماجد بن صالح الثنيان</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4859,7 +4859,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4933,7 +4933,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ…ظٹط¯</t>
+          <t>ثامر عبدالرحمن عبدالعزيز الحميد</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5081,7 +5081,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5118,7 +5118,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5192,7 +5192,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5229,7 +5229,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† طµط§ظ„ط­ ط­ظ…ط¯ ط§ظ„ط¯ط®ظٹظ„</t>
+          <t>ريان صالح حمد الدخيل</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5340,7 +5340,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5377,7 +5377,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5488,7 +5488,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5599,7 +5599,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ„ظˆظ‡</t>
+          <t>بسام عبدالرحمن بن صالح الحلوه</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5673,7 +5673,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5747,7 +5747,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5784,7 +5784,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5821,7 +5821,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5858,7 +5858,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ظپظٹطµظ„ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط²ظˆظٹط¯</t>
+          <t>فهد فيصل بن عبدالله الزويد</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5932,7 +5932,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6117,7 +6117,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6154,7 +6154,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6191,7 +6191,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ط«ط§ظ…ط± ط§ط­ظ…ط¯ ط¨ظ† ط¹ظ…ظٹط± ط§ظ„ط¹ظ…ظٹط±</t>
+          <t>ثامر احمد بن عمير العمير</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6228,7 +6228,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6265,7 +6265,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6376,7 +6376,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6487,7 +6487,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط§ظ…ط± ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹ط§ظ…ط±</t>
+          <t>عبدالله عامر بن عبدالله العامر</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6598,7 +6598,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -6635,7 +6635,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6783,7 +6783,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط´ظٹظ‚ط­</t>
+          <t>ريان خالد سليمان المشيقح</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6820,7 +6820,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -6857,7 +6857,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6894,7 +6894,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -7005,7 +7005,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7042,7 +7042,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ظ…ط­ظ…ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف محمد الحربي</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -7116,7 +7116,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ط·ط±ظپظٹط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>طرفيات الحاسب</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7153,7 +7153,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ طµظٹط§ظ†ط© ط§ظ„ط­ط§ط³ط¨</t>
+          <t>مهارات صيانة الحاسب</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7190,7 +7190,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ط´ط¨ظƒط§طھ ط§ظ„ط­ط§ط³ط¨</t>
+          <t>شبكات الحاسب</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>طھظ…ط¯ظٹط¯ ظƒظٹط§ط¨ظ„ ط§ظ„ط§ظ„ظٹط§ظپ ط§ظ„ط¶ظˆط¦ظٹط©</t>
+          <t>تمديد كيابل الالياف الضوئية</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7264,7 +7264,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ظ†ط¸ط§ظ… طھط´ط؛ظٹظ„ ط§ظ„ط´ط¨ظƒط©-2</t>
+          <t>نظام تشغيل الشبكة-2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>طھط¯ط±ظٹط¨ ط¥ظ†طھط§ط¬ظٹ</t>
+          <t>تدريب إنتاجي</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -7338,7 +7338,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -7375,7 +7375,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط© - 3</t>
+          <t>أنشطة مهنية - 3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظ…ط­ظ…ط¯ ط§ظ„ط·ظˆظٹط±ط¨</t>
+          <t>محمد عبدالرحمن محمد الطويرب</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -7449,7 +7449,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -7486,7 +7486,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -7560,7 +7560,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -7597,7 +7597,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -7671,7 +7671,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>زياد عبدالله بن عبيد الحربي</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -7782,7 +7782,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -7856,7 +7856,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -7893,7 +7893,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -7930,7 +7930,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ظ…طھط¹ط¨ ط¹ظˆط§ط¶ ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط¹ظ…ظٹط±ظٹ</t>
+          <t>متعب عواض ربيعان العميري</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8004,7 +8004,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8041,7 +8041,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -8078,7 +8078,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -8115,7 +8115,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8226,7 +8226,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8263,7 +8263,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظ…ط­ظ…ط¯ ط¨ظ† ظ…ط§ط´ط¹ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فارس محمد بن ماشع المطيري</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8300,7 +8300,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -8374,7 +8374,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -8411,7 +8411,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -8448,7 +8448,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -8485,7 +8485,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -8522,7 +8522,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -8596,7 +8596,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -8633,7 +8633,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ط¹ظ…ظٹط± ط­ظ…ط¯ط§ظ† ظ†ط§ط¦ط´ ط§ظ„ط؛ط§ظ…ط¯ظٹ</t>
+          <t>عمير حمدان نائش الغامدي</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -8670,7 +8670,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -8707,7 +8707,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -8744,7 +8744,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -8781,7 +8781,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -8892,7 +8892,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -8929,7 +8929,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9003,7 +9003,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ط³ط¹ط¯ ظ…ظپط±ط­ ط¨ظ† ط³ط¹ط¯ ط§ظ„ط´ظ…ط±ظٹ</t>
+          <t>سعد مفرح بن سعد الشمري</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9040,7 +9040,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9077,7 +9077,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9114,7 +9114,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9151,7 +9151,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -9225,7 +9225,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -9299,7 +9299,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -9336,7 +9336,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -9373,7 +9373,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ط³ط¹ظˆط¯ ط­ط³ظ† ط¨ظ† ط¬ظ‡ط² ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سعود حسن بن جهز الحربي</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -9410,7 +9410,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -9484,7 +9484,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -9558,7 +9558,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -9632,7 +9632,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -9669,7 +9669,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -9706,7 +9706,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -9743,7 +9743,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ظ…ط§ط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط§ط­ظ…ط¯ ط§ظ„ظ…ط§ظ„ظƒ</t>
+          <t>مازن عبدالله بن احمد المالك</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -9780,7 +9780,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ظ…ظپطھظˆط­ط© ط§ظ„ظ…طµط¯ط±</t>
+          <t>تطبيقات مفتوحة المصدر</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -9817,7 +9817,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ظ…ط¨ط§ط¯ط¦ ظ‚ظˆط§ط¹ط¯ ط§ظ„ط¨ظٹط§ظ†ط§طھ</t>
+          <t>مبادئ قواعد البيانات</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -9854,7 +9854,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ظ…ظƒظˆظ†ط§طھ ط§ظ„ط­ط§ط³ط¨-2</t>
+          <t>مكونات الحاسب-2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -9891,7 +9891,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¨ط±ظ…ط¬ط©-1</t>
+          <t>لغة برمجة-1</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -9928,7 +9928,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ط±ط³ظ… ط§ظ„ط´ط¨ظƒط§طھ ط¨ط§ظ„ط­ط§ط³ط¨</t>
+          <t>رسم الشبكات بالحاسب</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -9965,7 +9965,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ظ†ط¸ط§ظ… ظ„ظٹظ†ظƒط³</t>
+          <t>أساسيات نظام لينكس</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10002,7 +10002,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ط³ظٹط§طھ ط§ظ„ط¥ظ„ظƒطھط±ظˆظ†ظٹط§طھ</t>
+          <t>أساسيات الإلكترونيات</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10039,7 +10039,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ط£ظ†ط´ط·ط© ظ…ظ‡ظ†ظٹط©</t>
+          <t>أنشطة مهنية</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط±ط§ط¶ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سلمان بن راضي الحربي</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10113,7 +10113,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10150,7 +10150,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10187,7 +10187,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10224,7 +10224,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -10298,7 +10298,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -10335,7 +10335,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -10372,7 +10372,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ظٹط²ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط±ط¨ظٹط´</t>
+          <t>يزن عبدالله بن محمد الربيش</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -10483,7 +10483,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -10520,7 +10520,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -10557,7 +10557,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -10594,7 +10594,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -10668,7 +10668,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -10779,7 +10779,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -10816,7 +10816,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ظ„ظٹ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط­ظƒظ…ظٹ</t>
+          <t>اياد علي عبدالله حكمي</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -10853,7 +10853,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -10890,7 +10890,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -10927,7 +10927,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -10964,7 +10964,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -11001,7 +11001,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11075,7 +11075,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11112,7 +11112,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -11149,7 +11149,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -11186,7 +11186,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>ط§ط¨ط±ط§ظ‡ظٹظ… ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط´طھظˆظٹ</t>
+          <t>ابراهيم عبدالرحمن ابراهيم الشتوي</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -11223,7 +11223,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -11260,7 +11260,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -11297,7 +11297,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -11371,7 +11371,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -11445,7 +11445,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -11482,7 +11482,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -11519,7 +11519,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -11556,7 +11556,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط³ظ„ظ…ط§ظ† ط¨ظ† ط¹ط§ظٹط¶ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>حمد سلمان بن عايض الرشيدي</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -11593,7 +11593,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ط³ظ„ظˆظƒ ظ…ظ‡ظ†ظٹ</t>
+          <t>سلوك مهني</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -11630,7 +11630,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ط«ظ‚ط§ظپط© ط¥ط³ظ„ط§ظ…ظٹط©-2</t>
+          <t>ثقافة إسلامية-2</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¥ظ†ط¬ظ„ظٹط²ظٹط© (2)</t>
+          <t>لغة إنجليزية (2)</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -11704,7 +11704,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ط§ظ„طھط±ط¨ظٹط© ط§ظ„ط¨ط¯ظ†ظٹط©-2</t>
+          <t>التربية البدنية-2</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -11741,7 +11741,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>طھط·ط¨ظٹظ‚ط§طھ ط§ظ„ط­ط§ط³ط¨ ط§ظ„ط¢ظ„ظٹ</t>
+          <t>تطبيقات الحاسب الآلي</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -11778,7 +11778,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ط¶ظٹط§طھ (2)</t>
+          <t>رياضيات (2)</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -11815,7 +11815,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ظ„ط؛ط© ط¹ط±ط¨ظٹط©-2</t>
+          <t>لغة عربية-2</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -11852,7 +11852,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ط§ط±ط§طھ ط§ظ„طھظˆط§طµظ„ ظˆط§ظ„طھط¹ط§ظˆظ†</t>
+          <t>مهارات التواصل والتعاون</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -11889,7 +11889,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ط§ظ„طھظپظƒظٹط± ط§ظ„ظ†ط§ظ‚ط¯ ظˆط§ظ„ط¥ط¨ط¯ط§ط¹ظٹ</t>
+          <t>التفكير الناقد والإبداعي</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ظˆط±ط´ طھط£ط³ظٹط³ظٹط©</t>
+          <t>ورش تأسيسية</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط£ط­ظ…ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>محمد أحمد بن محمد السالم</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ط±ط§ظƒط§ظ† ط®ط§ظ„ط¯ ظ†ط§ظٹظپ ط§ظ„ط¹طھظٹط¨ظٹ</t>
+          <t>راكان خالد نايف العتيبي</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -12000,7 +12000,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط®ط§ظ„ط¯ ط¨ظ† ط¹ظ„ظٹ ط§ظ„ظ†ط؛ظٹظ…ط´ظٹ</t>
+          <t>عبدالله خالد بن علي النغيمشي</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -12037,7 +12037,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ط³ظپظٹط§ظ† ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ظ„ظ…ظ‚ط¨ظ„</t>
+          <t>سفيان محمد عبدالرحمن المقبل</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -12074,7 +12074,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ظ„ط²ظˆظٹط¯</t>
+          <t>عبدالرحمن عبدالعزيز عبدالرحمن الزويد</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -12111,7 +12111,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ظ…ط§ظ„ظƒ ط¹ط²ظٹط² ظ…ط±ظٹط¨ط¯ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>مالك عزيز مريبد الرشيدي</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -12148,7 +12148,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط­ظ†ط§ظٹط§</t>
+          <t>عبدالعزيز عبدالرحمن بن عبدالعزيز الحنايا</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -12185,7 +12185,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>ط§ط³ط§ظ…ظ‡ ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط¹طھظٹط¨ظٹ</t>
+          <t>اسامه محمد عبدالله العتيبي</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -12222,7 +12222,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>ظپط±ط§ط³ ط³ظ…ط±ط§ظ† ط³ط¹ظٹظپط§ظ† ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>فراس سمران سعيفان المطيري</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -12259,7 +12259,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>ط¹ط²ط§ظ… ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط³ظ„ظٹظ…ط§ظ† ط§ظ„ط¯ط¨ظٹط®ظٹ</t>
+          <t>عزام عبدالله بن سليمان الدبيخي</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>ظ‡ط´ط§ظ… ظ…ط­ط³ظ† ط²ط¨ط§ط± ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>هشام محسن زبار الحربي</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -12333,7 +12333,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>ظ‡ط§ظ†ظٹ ظ…ط¹ط²ظٹ ط¹ط§ظٹط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>هاني معزي عايد الحربي</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -12370,7 +12370,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>ط³ط§ظ„ظ… ط؛ط²ط§ظٹ ط¨ظ† ط­ظ…ظˆط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>سالم غزاي بن حمود الحربي</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>ظپظ‡ط¯ ط¹ظ„ظٹ ط¨ظ† ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ظ„ط´ط­ظٹطھط§ظ†</t>
+          <t>فهد علي بن عبدالرحمن الشحيتان</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -12444,7 +12444,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ط­ط§طھظ… ظ†ط§ظٹظپ ط¨ظ† ط­ط³ظٹظ† ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>حاتم نايف بن حسين الحربي</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -12481,7 +12481,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ظ…ط¯</t>
+          <t>عبدالرحمن عبدالله بن صالح الحمد</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -12518,7 +12518,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ظˆظ„ظٹط¯ ظ…ظ†ظˆط± ظ…ظ†ط§ظˆط± ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>وليد منور مناور الحربي</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -12555,7 +12555,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ط³ظ„ظٹظ…ط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط³ظ„ظٹظ…ط§ظ† ط§ظ„ط¹ظ„ظٹط§ظ†</t>
+          <t>سليمان عبدالله بن سليمان العليان</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¹ط¨ظٹط¯ط§ظ„ظ„ظ‡ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ†ط²ظٹ</t>
+          <t>عبدالعزيز عبيدالله محمد العنزي</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>ط¬ظ‡ط§ط¯ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط³ط§ظ„ظ…</t>
+          <t>جهاد عبدالرحمن عبدالله السالم</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -12666,7 +12666,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>ط§ظ„ظ…ط«ظ†ظ‰ طµط§ظ„ط­ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ظ…ط²ظٹط±ط¹ظٹ</t>
+          <t>المثنى صالح عبدالله المزيرعي</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -12703,7 +12703,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ط­ط³ظٹظ† ظ…ط­ظ…ط¯ ط¬ط§ط²ظٹ ط§ظ„ط­ط±ط¨ظ‰</t>
+          <t>حسين محمد جازي الحربى</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -12740,7 +12740,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>ط¨ط§ط³ظ„ ط§ط­ظ…ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ظ…ط­ظٹط³ظ†</t>
+          <t>باسل احمد بن صالح المحيسن</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -12777,7 +12777,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>ظˆط§ظٹظ„ ط³ط¹ط¯ ط¨ظ† ظ…ط­ظ…ط¯ ط§ط¨ط§ظ„ط±ظˆط³</t>
+          <t>وايل سعد بن محمد ابالروس</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ظ…ط­ط³ظ† ط²ط¨ط§ط± ط§ظ„ظˆظ‡ط¨ظٹ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>عبدالله محسن زبار الوهبي الحربي</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -12851,7 +12851,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط«ظ…ط§ظ† ط­ظ…ط¯ ط§ظ„ظ†ظ…ظٹط±</t>
+          <t>عبدالله عثمان حمد النمير</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -12888,7 +12888,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>طµط§ظ„ط­ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط®ظ„ظپ ط§ظ„ط¹ظ†ط²ظ‰</t>
+          <t>صالح عبدالله خلف العنزى</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -12925,7 +12925,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>ط£ط³ط§ظ…ظ‡ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ظ„ظ…ظ†طµظˆط±</t>
+          <t>أسامه عبدالله بن عبدالرحمن المنصور</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -12962,7 +12962,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>ظ…ظ‡ظ†ط¯ ط³ظ„ظٹظ…ط§ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ظˆظٹط­</t>
+          <t>مهند سليمان محمد السويح</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -12999,7 +12999,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>ط¹ظ…ط± طµط§ظ„ط­ ط¨ظ† ط³ظ„ظٹظ…ط§ظ† ط§ظ„ط؛ط§ظ†ظ…</t>
+          <t>عمر صالح بن سليمان الغانم</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -13036,7 +13036,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ظ…ط­ظ…ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط³ظ„ط§ظ…ظ‡</t>
+          <t>عبدالله محمد عبدالله السلامه</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -13073,7 +13073,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>ط§ظٹط§ط¯ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط³ظˆظ†</t>
+          <t>اياد عبدالعزيز بن عبدالله الحسون</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -13110,7 +13110,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ط­ظ…ط¯ ط³ظ„ظٹظ…ط§ظ† ط§ظ„ط¹ظ†ط§ط²</t>
+          <t>زياد حمد سليمان العناز</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ طµط§ظ„ط­ ط¨ظ† ظ…ط¨ط§ط±ظƒ ط§ظ„ظ…ط­ظٹظ…ظٹط¯</t>
+          <t>عبدالله صالح بن مبارك المحيميد</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>ظˆظ„ظٹط¯ ظ…ط§ط¬ط¯ ط·ظ„ظ‚ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>وليد ماجد طلق الحربي</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -13221,7 +13221,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>ظٹط§ط³ط± ظ…ط­ظ…ط¯ ط¨ظ† ط®ط§ظ„ط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ياسر محمد بن خالد الحربي</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -13258,7 +13258,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>ظپط§ظٹط² ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ظپط§ظٹط² ط§ظ„ظپط§ظٹط²</t>
+          <t>فايز عبدالرحمن فايز الفايز</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -13295,7 +13295,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>ط­ظ…ط¯ ط«ظˆظٹظ†ظٹ طµط§ظ„ط­ ط§ظ„ط«ظˆظٹظ†ظٹ</t>
+          <t>حمد ثويني صالح الثويني</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -13332,7 +13332,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>ظ…ط§ط¬ط¯ طµط§ظ„ط­ ظ…ط­ظ…ط¯ ط§ظ„ظˆظ„ظٹط¹ظ‰</t>
+          <t>ماجد صالح محمد الوليعى</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -13369,7 +13369,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>ظٹظˆط³ظپ ظ…ط­ظ…ط¯ ط¨ظ† ط³ظ…ظٹط± ط§ظ„ط®ظ…ط´ظٹ</t>
+          <t>يوسف محمد بن سمير الخمشي</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -13406,7 +13406,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ…ط¬ظٹط¯ ط±ظƒط¨ط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>عبدالمجيد ركبان عبدالله الحربي</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -13443,7 +13443,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ط¨ط³ط§ظ… ظ…ط­ظ…ط¯ ط¬ط¯ظٹط¹ ط§ظ„ط®ظ…ط´ظٹ</t>
+          <t>بسام محمد جديع الخمشي</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -13480,7 +13480,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>ظƒط§ظٹط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ظٹط³ظ‰ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>كايد عبدالله عيسى الحربي</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -13517,7 +13517,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ط­ط³ط§ظ… ط³ظ„ظٹظ…ط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط³ظˆظٹط¯</t>
+          <t>حسام سليمان عبدالله السويد</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -13554,7 +13554,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>ط®ط§ظ„ط¯ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ظ„ظٹ ط§ظ„ظ…ظˆط³ظ‰</t>
+          <t>خالد عبدالله علي الموسى</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -13591,7 +13591,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>ظپط±ط§ط³ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط³ظ„ط·ط§ظ†</t>
+          <t>فراس عبدالله بن محمد السلطان</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -13628,7 +13628,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ط®ط§ظ„ط¯ ط³ظ„ظٹظ…ط§ظ† ط±ط¨ظٹط¹ط§ظ† ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>خالد سليمان ربيعان الحربي</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -13665,7 +13665,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>ط£ط­ظ…ط¯ ط®ط§ظ„ط¯ ط¨ظ† ط­ظ…ظˆط¯ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>أحمد خالد بن حمود الحربي</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -13702,7 +13702,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ط³ظ„ظٹظ…ط§ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط³ط¹ظٹط¯ ط§ظ„ط³ط¹ظٹط¯</t>
+          <t>سليمان عبدالله سعيد السعيد</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -13739,7 +13739,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ط£ظ†ط³ ظ…ط·ط± ط¹ظˆط¶ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>أنس مطر عوض الحربي</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -13776,7 +13776,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>ظ…ظ‚ط¨ظ„ ط³ط§ظ„ظ… ظ…ظ‚ط¨ظ„ ط§ظ„ط¹ظ†ط²ظٹ</t>
+          <t>مقبل سالم مقبل العنزي</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>ظپظٹطµظ„ ط¨ط±ظƒظ‰ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>فيصل بركى بن عبدالله الرشيدي</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ظپظ‡ط¯ ط§ظ„ط¹ط«ظٹظ…</t>
+          <t>عبدالرحمن ابراهيم فهد العثيم</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -13887,7 +13887,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط®ظ„ظپ ط³ظ…ظٹط± ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد خلف سمير الحربي</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -13924,7 +13924,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>طھط±ظƒظٹ ط®ط§ظ„ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط­ط³ظٹظ†ط§ظ†</t>
+          <t>تركي خالد بن صالح الحسينان</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -13961,7 +13961,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¨ط§ط±ظٹ ظپظ‡ط¯ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط®ط·ظٹط¨</t>
+          <t>عبدالباري فهد عبدالعزيز الخطيب</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -13998,7 +13998,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ظ‡ظ„ظٹظ„ طµط§ظ„ط­ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>ريان هليل صالح الحربي</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -14035,7 +14035,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>ط±ظٹط§ظ† ط³ظ„ظٹظ…ط§ظ† ط¨ظ† ط­ظ…ط¯ ط§ظ„ط´ظ‚ط§ظˆظٹ</t>
+          <t>ريان سليمان بن حمد الشقاوي</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -14072,7 +14072,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ظپظ‡ط¯ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„طµظˆظٹظ„ط­</t>
+          <t>عبدالعزيز فهد عبدالعزيز الصويلح</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -14109,7 +14109,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>ظ…طµط¹ط¨ ظ…ط­ظ…ط¯ ط­ظ…ظˆط¯ ط§ظ„طھظˆظٹط¬ط±ظٹ</t>
+          <t>مصعب محمد حمود التويجري</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -14146,7 +14146,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط³ظ†ط¯ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>عبدالعزيز عبدالله سند المطيري</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -14183,7 +14183,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ط³ظٹظپ ط¹ظˆط¶ ط®ظ†ظٹظپط± ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>سيف عوض خنيفر الرشيدي</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -14220,7 +14220,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط³ط¹ط¯ ط¨ظ† ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>عبدالعزيز سعد بن عبدالله الرشيدي</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -14257,7 +14257,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط³ظ„ظٹظ…ط§ظ† ط¹ط¨ظٹط¯ط§ظ„ظ„ظ‡ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>محمد سليمان عبيدالله الحربي</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ط­ط³ط§ظ… ط§ط­ظ…ط¯ ظٹط­ظٹظ‰ ط¬ط­ظپظ„ظٹ</t>
+          <t>حسام احمد يحيى جحفلي</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -14331,7 +14331,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ظ…ط¨ظ„ط¬ ظ†ظ…ط§ط، ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>عبدالله مبلج نماء الرشيدي</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -14368,7 +14368,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ط¹ظٹط¯ ظ…ط¨ط§ط±ظƒ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>محمد عيد مبارك الرشيدي</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -14405,7 +14405,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>ط³ظ„ظٹظ…ط§ظ† ظ…ط­ظ…ط¯ ط¨ظ† ط³ظ„ظٹظ…ط§ظ† ط§ظ„ظ…ط³ظٹط·ظٹط±</t>
+          <t>سليمان محمد بن سليمان المسيطير</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -14442,7 +14442,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ط®ط§ظ„ط¯ ط­ط§ط¨ط³ ط¨ظ† ظ…ط¹ظٹط¶ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>خالد حابس بن معيض الحربي</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -14479,7 +14479,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>ط±ط§ظ…ظٹ ط±ط§ط´ط¯ ط¹ط¨ط¯ط§ظ„ط¹ط²ظٹط² ط§ظ„ط¶ط­ظٹط§ظ†</t>
+          <t>رامي راشد عبدالعزيز الضحيان</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -14516,7 +14516,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>ظپط§ط±ط³ ظپط±ظٹط­ ط¹ظٹط¯ ط§ظ„ط±ط´ظٹط¯ظٹ</t>
+          <t>فارس فريح عيد الرشيدي</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -14553,7 +14553,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>ط¨ظ„ط§ظ„ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¹ط¨ط¯ط§ظ„ط®ط§ظ„ظ‚ ط¹ط¨ط¯ط§ظ„ظ‚ط§ط¯ط±</t>
+          <t>بلال عبدالرحمن عبدالخالق عبدالقادر</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -14590,7 +14590,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ط­ظƒظٹظ… ط­ظ…ط¯ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط³ظ„ط§ظ…ظ‡</t>
+          <t>عبدالحكيم حمد بن صالح السلامه</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -14627,7 +14627,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>ظ…ط­ظ…ط¯ ظ…ط³ط¹ظˆط¯ ظ…ط­ظ…ط¯ ط§ظ„ط¹ظ‚ظٹظ„</t>
+          <t>محمد مسعود محمد العقيل</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -14664,7 +14664,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ظپط±ط§ط³ ظپظˆط§ط² ظپظ‡ط¯ ط§ظ„ط¬ط§ظ„ط³</t>
+          <t>فراس فواز فهد الجالس</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -14701,7 +14701,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ظˆظ„ظٹط¯ ظ…ظ„ظٹط­ طµط§ظ„ط­ ط§ظ„ظ…ط³ط§ط¹ط¯</t>
+          <t>وليد مليح صالح المساعد</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -14738,7 +14738,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>ط¹ط§طµظ… ط¨ط±ط§ظƒ ط¨ظ† طµط§ظ„ط­ ط§ظ„ط¨ط±ط§ظƒ</t>
+          <t>عاصم براك بن صالح البراك</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -14775,7 +14775,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>ظ…ط´ط§ط±ظٹ ط¹ط§ط¨ط¯ ط¨ظ† ط¹ظˆط¶  ط§ظ„ظ„ظ‡ ط§ظ„ظ…ط·ظٹط±ظٹ</t>
+          <t>مشاري عابد بن عوض  الله المطيري</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -14812,7 +14812,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ظ…ظ†طµظˆط± ظ…ظˆط³ظ‰ ظ†ط§طµط± ط§ظ„ظ‡ط²ط§ط¹</t>
+          <t>منصور موسى ناصر الهزاع</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -14849,7 +14849,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>ط³ظ„ظٹظ…ط§ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط¨ظ† ظ…ط­ظ…ط¯ ط§ظ„ط´ط¨ظ„</t>
+          <t>سليمان ابراهيم بن محمد الشبل</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ط·ظٹظپ ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¨ظ† ط­ط¨ظٹظ„ ط§ظ„ط­ط±ط¨ظٹ</t>
+          <t>عبداللطيف عبدالله بن حبيل الحربي</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -14923,7 +14923,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ط²ظٹط§ط¯ ظٹط­ظ‰ ط¨ظ† طµط¯ظٹظ‚ ط­ظ…ط¯ظٹ</t>
+          <t>زياد يحى بن صديق حمدي</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -14960,7 +14960,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ط¥ط¯ط®ط§ظ„ ط§ظ„ط¨ظٹط§ظ†ط§طھ ظˆظ…ط¹ط§ظ„ط¬ط© ط§ظ„ظ†طµظˆطµ</t>
+          <t>إدخال البيانات ومعالجة النصوص</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ط¹ط¨ط¯ط§ظ„ظ„ظ‡ ط¹ط¨ط¯ط§ظ„ط±ط­ظ…ظ† ط¨ظ† ط§ط¨ط±ط§ظ‡ظٹظ… ط§ظ„ط¨ط§ط­ظˆط«</t>
+          <t>عبدالله عبدالرحمن بن ابراهيم الباحوث</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -471,22 +471,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1174,22 +1174,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1285,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1618,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1729,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1951,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2284,22 +2284,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2469,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2876,22 +2876,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3061,22 +3061,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3283,22 +3283,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4023,22 +4023,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4171,22 +4171,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4430,22 +4430,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4837,22 +4837,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5133,22 +5133,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5725,22 +5725,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6613,22 +6613,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7279,22 +7279,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7501,22 +7501,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7797,22 +7797,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7908,22 +7908,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8130,22 +8130,22 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8685,22 +8685,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8796,22 +8796,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8907,22 +8907,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9536,22 +9536,22 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9647,22 +9647,22 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9869,22 +9869,22 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -9980,22 +9980,22 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10202,22 +10202,22 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10239,22 +10239,22 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10609,22 +10609,22 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10720,22 +10720,22 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10757,22 +10757,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -10979,22 +10979,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11090,22 +11090,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11312,22 +11312,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11349,22 +11349,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11460,22 +11460,22 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11497,22 +11497,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11534,22 +11534,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11645,22 +11645,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11904,22 +11904,22 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12015,22 +12015,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12274,22 +12274,22 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12496,22 +12496,22 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12533,22 +12533,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12644,22 +12644,22 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12792,22 +12792,22 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13051,22 +13051,22 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13421,22 +13421,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13569,22 +13569,22 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13606,22 +13606,22 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13754,22 +13754,22 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13902,22 +13902,22 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14309,22 +14309,22 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14531,22 +14531,22 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14642,22 +14642,22 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14827,22 +14827,22 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1174,22 +1174,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1507,22 +1507,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1618,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1729,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1803,22 +1803,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>18.42</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>15.79</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>13.16</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -1951,22 +1951,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2025,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2173,22 +2173,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2247,22 +2247,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2284,22 +2284,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2950,22 +2950,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3912,22 +3912,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4171,22 +4171,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4430,22 +4430,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4541,22 +4541,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4948,22 +4948,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5170,22 +5170,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6058,22 +6058,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6909,22 +6909,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7131,22 +7131,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7242,22 +7242,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7279,22 +7279,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8648,22 +8648,22 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8685,22 +8685,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8722,22 +8722,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8759,22 +8759,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8870,22 +8870,22 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8944,22 +8944,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -8981,22 +8981,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9388,22 +9388,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9425,22 +9425,22 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9499,22 +9499,22 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9684,22 +9684,22 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9758,22 +9758,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9869,22 +9869,22 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10054,22 +10054,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10128,22 +10128,22 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10461,22 +10461,22 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10498,22 +10498,22 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10868,22 +10868,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11238,22 +11238,22 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11275,22 +11275,22 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11312,22 +11312,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11423,22 +11423,22 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11497,22 +11497,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11534,22 +11534,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11793,22 +11793,22 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12015,22 +12015,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12052,22 +12052,22 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12089,22 +12089,22 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12237,22 +12237,22 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12274,22 +12274,22 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12311,22 +12311,22 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12348,22 +12348,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12422,22 +12422,22 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12459,22 +12459,22 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12496,22 +12496,22 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12533,22 +12533,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12644,22 +12644,22 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12792,22 +12792,22 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12829,22 +12829,22 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12940,22 +12940,22 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13014,22 +13014,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13051,22 +13051,22 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13421,22 +13421,22 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13569,22 +13569,22 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13606,22 +13606,22 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13754,22 +13754,22 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13828,22 +13828,22 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13902,22 +13902,22 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14013,22 +14013,22 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14309,22 +14309,22 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14383,22 +14383,22 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14531,22 +14531,22 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14642,22 +14642,22 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14679,22 +14679,22 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14716,22 +14716,22 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14827,22 +14827,22 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
